--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E42AC3-78BE-6C4F-A536-5EE7CED8A179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810343AC-358D-E34F-8539-29D1A1767F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AS32"/>
+  <dimension ref="A1:AT32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,14 +726,17 @@
       <c r="AS1" s="6">
         <v>46268</v>
       </c>
+      <c r="AT1" s="6">
+        <v>46269</v>
+      </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
@@ -745,7 +748,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -872,18 +875,21 @@
       <c r="AS2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AT2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1018,18 +1024,21 @@
       <c r="AS3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1164,18 +1173,21 @@
       <c r="AS4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1310,18 +1322,21 @@
       <c r="AS5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1456,14 +1471,17 @@
       <c r="AS6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -1487,7 +1505,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1602,14 +1620,17 @@
       <c r="AS7" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AT7" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1625,7 +1646,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1748,18 +1769,21 @@
       <c r="AS8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AT8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1894,14 +1918,17 @@
       <c r="AS9" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="AT9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
@@ -1917,7 +1944,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
@@ -2040,18 +2067,21 @@
       <c r="AS10" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AT10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2186,18 +2216,21 @@
       <c r="AS11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2332,18 +2365,21 @@
       <c r="AS12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2478,18 +2514,21 @@
       <c r="AS13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2624,14 +2663,17 @@
       <c r="AS14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
@@ -2655,7 +2697,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2770,14 +2812,17 @@
       <c r="AS15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AT15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -2801,7 +2846,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2916,18 +2961,21 @@
       <c r="AS16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AT16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -3062,18 +3110,21 @@
       <c r="AS17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3208,14 +3259,17 @@
       <c r="AS18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -3231,7 +3285,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -3354,18 +3408,21 @@
       <c r="AS19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AT19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3500,14 +3557,17 @@
       <c r="AS20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
@@ -3531,7 +3591,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3646,14 +3706,17 @@
       <c r="AS21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AT21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -3677,7 +3740,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -3792,18 +3855,21 @@
       <c r="AS22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AT22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -3938,18 +4004,21 @@
       <c r="AS23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4084,18 +4153,21 @@
       <c r="AS24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4230,18 +4302,21 @@
       <c r="AS25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4376,18 +4451,21 @@
       <c r="AS26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4516,18 +4594,21 @@
       <c r="AS27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4650,18 +4731,21 @@
       <c r="AS28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4730,14 +4814,17 @@
       <c r="AS29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -4753,7 +4840,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -4810,18 +4897,21 @@
       <c r="AS30" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="AT30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4890,8 +4980,11 @@
       <c r="AS31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AT31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810343AC-358D-E34F-8539-29D1A1767F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8405EF8-339C-D749-8F87-E6238F52C2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AT32"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,18 +729,27 @@
       <c r="AT1" s="6">
         <v>46269</v>
       </c>
+      <c r="AU1" s="6">
+        <v>46272</v>
+      </c>
+      <c r="AV1" s="6">
+        <v>46273</v>
+      </c>
+      <c r="AW1" s="6">
+        <v>46274</v>
+      </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -748,7 +757,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E26" si="0">COUNTIF(K2:VS2,"A")</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F26" si="1">COUNTIF(K2:VT2,"B")</f>
@@ -864,32 +873,41 @@
         <v>18</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AT2" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1027,18 +1045,27 @@
       <c r="AT3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1176,18 +1203,27 @@
       <c r="AT4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1325,18 +1361,27 @@
       <c r="AT5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1474,18 +1519,27 @@
       <c r="AT6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1505,7 +1559,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1623,14 +1677,23 @@
       <c r="AT7" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AU7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW7" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1646,7 +1709,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1772,18 +1835,27 @@
       <c r="AT8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AU8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -1921,18 +1993,27 @@
       <c r="AT9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -1944,7 +2025,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
@@ -2068,20 +2149,29 @@
         <v>44</v>
       </c>
       <c r="AT10" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="AU10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW10" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2219,18 +2309,27 @@
       <c r="AT11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2368,18 +2467,27 @@
       <c r="AT12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2517,18 +2625,27 @@
       <c r="AT13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2666,18 +2783,27 @@
       <c r="AT14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2697,7 +2823,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2815,18 +2941,27 @@
       <c r="AT15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AU15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2846,7 +2981,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -2964,18 +3099,27 @@
       <c r="AT16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AU16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -3113,18 +3257,27 @@
       <c r="AT17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3262,18 +3415,27 @@
       <c r="AT18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3285,7 +3447,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -3409,20 +3571,29 @@
         <v>44</v>
       </c>
       <c r="AT19" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
+      </c>
+      <c r="AU19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW19" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3438,7 +3609,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
@@ -3560,18 +3731,27 @@
       <c r="AT20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3591,7 +3771,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3709,18 +3889,27 @@
       <c r="AT21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AU21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -3858,14 +4047,23 @@
       <c r="AT22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AU22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -3881,7 +4079,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4007,18 +4205,27 @@
       <c r="AT23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW23" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4156,18 +4363,27 @@
       <c r="AT24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4305,18 +4521,27 @@
       <c r="AT25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4454,18 +4679,27 @@
       <c r="AT26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4473,7 +4707,7 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
@@ -4597,18 +4831,27 @@
       <c r="AT27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4734,18 +4977,27 @@
       <c r="AT28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -4817,18 +5069,27 @@
       <c r="AT29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -4900,18 +5161,27 @@
       <c r="AT30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AU30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -4931,7 +5201,7 @@
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="35">COUNTIF(K31:VV31,"R")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="36">COUNTIF(K31:VW31,"RH")</f>
@@ -4983,8 +5253,17 @@
       <c r="AT31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AU31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW31" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8405EF8-339C-D749-8F87-E6238F52C2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74216180-3F1A-3D45-A01F-AA8B9CFC438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +583,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -738,18 +737,27 @@
       <c r="AW1" s="6">
         <v>46274</v>
       </c>
+      <c r="AX1" s="6">
+        <v>46275</v>
+      </c>
+      <c r="AY1" s="6">
+        <v>46279</v>
+      </c>
+      <c r="AZ1" s="6">
+        <v>46280</v>
+      </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -896,18 +904,27 @@
       <c r="AW2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1054,18 +1071,27 @@
       <c r="AW3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1212,18 +1238,27 @@
       <c r="AW4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1370,18 +1405,27 @@
       <c r="AW5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1528,18 +1572,27 @@
       <c r="AW6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1559,7 +1612,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1686,14 +1739,23 @@
       <c r="AW7" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AX7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1709,7 +1771,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1844,18 +1906,27 @@
       <c r="AW8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AX8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AZ8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2002,18 +2073,27 @@
       <c r="AW9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2160,18 +2240,27 @@
       <c r="AW10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2318,18 +2407,27 @@
       <c r="AW11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2476,18 +2574,27 @@
       <c r="AW12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2634,18 +2741,27 @@
       <c r="AW13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2792,18 +2908,27 @@
       <c r="AW14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -2823,7 +2948,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -2950,18 +3075,27 @@
       <c r="AW15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AX15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -2981,7 +3115,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -3108,18 +3242,27 @@
       <c r="AW16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AX16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -3266,18 +3409,27 @@
       <c r="AW17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3424,18 +3576,27 @@
       <c r="AW18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3582,18 +3743,27 @@
       <c r="AW19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -3740,18 +3910,27 @@
       <c r="AW20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -3771,7 +3950,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -3898,18 +4077,27 @@
       <c r="AW21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AX21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -4056,14 +4244,23 @@
       <c r="AW22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -4079,7 +4276,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4214,18 +4411,27 @@
       <c r="AW23" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AX23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AY23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AZ23" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4372,18 +4578,27 @@
       <c r="AW24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4530,18 +4745,27 @@
       <c r="AW25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4688,18 +4912,27 @@
       <c r="AW26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -4840,18 +5073,27 @@
       <c r="AW27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -4986,18 +5228,27 @@
       <c r="AW28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -5078,18 +5329,27 @@
       <c r="AW29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -5170,18 +5430,27 @@
       <c r="AW30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="AX30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -5201,7 +5470,7 @@
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="35">COUNTIF(K31:VV31,"R")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="36">COUNTIF(K31:VW31,"RH")</f>
@@ -5262,8 +5531,17 @@
       <c r="AW31" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="AX31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74216180-3F1A-3D45-A01F-AA8B9CFC438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF18E2-ECA7-7F46-B9C7-6FC02F8532E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -583,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:BC32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:55" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,18 +747,27 @@
       <c r="AZ1" s="6">
         <v>46280</v>
       </c>
+      <c r="BA1" s="6">
+        <v>46281</v>
+      </c>
+      <c r="BB1" s="6">
+        <v>46282</v>
+      </c>
+      <c r="BC1" s="6">
+        <v>46283</v>
+      </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -913,18 +923,27 @@
       <c r="AZ2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1080,18 +1099,27 @@
       <c r="AZ3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1247,18 +1275,27 @@
       <c r="AZ4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1414,18 +1451,27 @@
       <c r="AZ5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1581,18 +1627,27 @@
       <c r="AZ6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1748,14 +1803,23 @@
       <c r="AZ7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1771,7 +1835,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1915,18 +1979,27 @@
       <c r="AZ8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BA8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BB8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2082,18 +2155,27 @@
       <c r="AZ9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2249,18 +2331,27 @@
       <c r="AZ10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2416,18 +2507,27 @@
       <c r="AZ11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2583,18 +2683,27 @@
       <c r="AZ12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2750,18 +2859,27 @@
       <c r="AZ13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -2917,14 +3035,23 @@
       <c r="AZ14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
@@ -2948,7 +3075,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -3084,14 +3211,23 @@
       <c r="AZ15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -3115,7 +3251,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -3251,18 +3387,27 @@
       <c r="AZ16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" si="4"/>
@@ -3274,7 +3419,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -3418,18 +3563,27 @@
       <c r="AZ17" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3585,18 +3739,27 @@
       <c r="AZ18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3752,14 +3915,23 @@
       <c r="AZ19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -3783,7 +3955,7 @@
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="7"/>
@@ -3919,14 +4091,23 @@
       <c r="AZ20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC20" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
@@ -3950,7 +4131,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -4086,14 +4267,23 @@
       <c r="AZ21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC21" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -4117,7 +4307,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -4253,14 +4443,23 @@
       <c r="AZ22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -4276,7 +4475,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4420,18 +4619,27 @@
       <c r="AZ23" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BA23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BB23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC23" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4587,18 +4795,27 @@
       <c r="AZ24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4606,7 +4823,7 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
@@ -4754,18 +4971,27 @@
       <c r="AZ25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BB25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -4921,18 +5147,27 @@
       <c r="AZ26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -5082,18 +5317,27 @@
       <c r="AZ27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -5237,18 +5481,27 @@
       <c r="AZ28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -5338,14 +5591,23 @@
       <c r="AZ29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -5361,7 +5623,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -5439,18 +5701,27 @@
       <c r="AZ30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BB30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -5540,8 +5811,17 @@
       <c r="AZ31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BA31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BC31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF18E2-ECA7-7F46-B9C7-6FC02F8532E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD6A171-5389-1946-ABAC-58E05C9E539D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BC32"/>
+  <dimension ref="A1:BE32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:57" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,18 +756,24 @@
       <c r="BC1" s="6">
         <v>46283</v>
       </c>
+      <c r="BD1" s="6">
+        <v>46286</v>
+      </c>
+      <c r="BE1" s="6">
+        <v>46287</v>
+      </c>
     </row>
-    <row r="2" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -932,18 +938,24 @@
       <c r="BC2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1108,18 +1120,24 @@
       <c r="BC3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1284,18 +1302,24 @@
       <c r="BC4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1460,18 +1484,24 @@
       <c r="BC5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1636,18 +1666,24 @@
       <c r="BC6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1812,14 +1848,20 @@
       <c r="BC7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1835,7 +1877,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -1988,18 +2030,24 @@
       <c r="BC8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BD8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2164,18 +2212,24 @@
       <c r="BC9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2340,18 +2394,24 @@
       <c r="BC10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2516,18 +2576,24 @@
       <c r="BC11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2692,18 +2758,24 @@
       <c r="BC12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2719,7 +2791,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="6"/>
@@ -2868,18 +2940,24 @@
       <c r="BC13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE13" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="14" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3044,18 +3122,24 @@
       <c r="BC14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3220,18 +3304,24 @@
       <c r="BC15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BD15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3396,14 +3486,20 @@
       <c r="BC16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BD16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -3419,7 +3515,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -3572,18 +3668,24 @@
       <c r="BC17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BD17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3748,18 +3850,24 @@
       <c r="BC18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -3924,14 +4032,20 @@
       <c r="BC19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -3943,7 +4057,7 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
@@ -4100,18 +4214,24 @@
       <c r="BC20" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BD20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BE20" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -4276,18 +4396,24 @@
       <c r="BC21" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BD21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -4452,14 +4578,20 @@
       <c r="BC22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BD22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -4475,7 +4607,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4628,18 +4760,24 @@
       <c r="BC23" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BD23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE23" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4804,18 +4942,24 @@
       <c r="BC24" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE24" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4980,18 +5124,24 @@
       <c r="BC25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -5156,14 +5306,20 @@
       <c r="BC26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
@@ -5179,7 +5335,7 @@
       </c>
       <c r="F27" s="3">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" ref="G27:G29" si="16">COUNTIF(K27:VU27,"M")</f>
@@ -5326,18 +5482,24 @@
       <c r="BC27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE27" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -5353,7 +5515,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="17"/>
@@ -5490,18 +5652,24 @@
       <c r="BC28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE28" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -5600,14 +5768,20 @@
       <c r="BC29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -5623,7 +5797,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -5710,18 +5884,24 @@
       <c r="BC30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BD30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -5820,8 +6000,14 @@
       <c r="BC31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BD31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BE31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD6A171-5389-1946-ABAC-58E05C9E539D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE30A4C-FCBB-C741-BEEA-E0C61D3C0F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -4943,10 +4943,10 @@
         <v>7</v>
       </c>
       <c r="BD24" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="BE24" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:57" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE30A4C-FCBB-C741-BEEA-E0C61D3C0F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3728A0-D9ED-094B-8FEE-2C2F267BE60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="53">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -584,13 +584,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BE32"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:61" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,18 +762,30 @@
       <c r="BE1" s="6">
         <v>46287</v>
       </c>
+      <c r="BF1" s="6">
+        <v>46288</v>
+      </c>
+      <c r="BG1" s="6">
+        <v>46290</v>
+      </c>
+      <c r="BH1" s="6">
+        <v>46293</v>
+      </c>
+      <c r="BI1" s="6">
+        <v>46294</v>
+      </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -944,18 +956,30 @@
       <c r="BE2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1126,18 +1150,30 @@
       <c r="BE3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1153,7 +1189,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="6"/>
@@ -1308,18 +1344,30 @@
       <c r="BE4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI4" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1490,18 +1538,30 @@
       <c r="BE5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1672,18 +1732,30 @@
       <c r="BE6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1854,14 +1926,26 @@
       <c r="BE7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1877,7 +1961,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2036,18 +2120,30 @@
       <c r="BE8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2059,7 +2155,7 @@
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="5"/>
@@ -2071,7 +2167,7 @@
       </c>
       <c r="I9" s="3">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="8"/>
@@ -2216,20 +2312,32 @@
         <v>7</v>
       </c>
       <c r="BE9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BH9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2245,7 +2353,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="6"/>
@@ -2400,18 +2508,30 @@
       <c r="BE10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI10" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2582,18 +2702,30 @@
       <c r="BE11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2609,7 +2741,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="6"/>
@@ -2764,18 +2896,30 @@
       <c r="BE12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2946,18 +3090,30 @@
       <c r="BE13" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BF13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3128,18 +3284,30 @@
       <c r="BE14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3310,18 +3478,30 @@
       <c r="BE15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3333,7 +3513,7 @@
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="5"/>
@@ -3492,14 +3672,26 @@
       <c r="BE16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI16" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -3515,7 +3707,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -3674,18 +3866,30 @@
       <c r="BE17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -3856,18 +4060,30 @@
       <c r="BE18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -4038,18 +4254,30 @@
       <c r="BE19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -4057,7 +4285,7 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
@@ -4220,18 +4448,30 @@
       <c r="BE20" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BF20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BG20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BH20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -4402,18 +4642,30 @@
       <c r="BE21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -4437,7 +4689,7 @@
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="8"/>
@@ -4584,14 +4836,26 @@
       <c r="BE22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI22" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -4607,7 +4871,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4766,14 +5030,26 @@
       <c r="BE23" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI23" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -4789,7 +5065,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -4948,18 +5224,30 @@
       <c r="BE24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -4975,7 +5263,7 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="6"/>
@@ -5130,18 +5418,30 @@
       <c r="BE25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI25" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -5312,18 +5612,30 @@
       <c r="BE26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -5347,7 +5659,7 @@
       </c>
       <c r="I27" s="3">
         <f t="shared" ref="I27:I29" si="18">COUNTIF(K27:VW27,"RH")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" ref="J27:J29" si="19">COUNTIF(K27:VW27,"S")</f>
@@ -5488,18 +5800,30 @@
       <c r="BE27" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BG27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BH27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -5515,7 +5839,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="17"/>
@@ -5658,18 +5982,30 @@
       <c r="BE28" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BF28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BG28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -5774,14 +6110,26 @@
       <c r="BE29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -5797,7 +6145,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -5890,18 +6238,30 @@
       <c r="BE30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BF30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BG30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -5917,7 +6277,7 @@
       </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31" si="34">COUNTIF(K31:VU31,"M")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="35">COUNTIF(K31:VV31,"R")</f>
@@ -6006,8 +6366,20 @@
       <c r="BE31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BF31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BG31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
         <v>0</v>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3728A0-D9ED-094B-8FEE-2C2F267BE60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EF626D-2241-854B-963D-7D8EB50A4343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="54">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>Glenn Manga-Tabi</t>
   </si>
 </sst>
 </file>
@@ -584,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BM32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:65" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,18 +777,30 @@
       <c r="BI1" s="6">
         <v>46294</v>
       </c>
+      <c r="BJ1" s="6">
+        <v>46295</v>
+      </c>
+      <c r="BK1" s="6">
+        <v>46297</v>
+      </c>
+      <c r="BL1" s="4">
+        <v>46300</v>
+      </c>
+      <c r="BM1" s="4">
+        <v>46301</v>
+      </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -968,18 +983,30 @@
       <c r="BI2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1162,18 +1189,30 @@
       <c r="BI3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1356,18 +1395,30 @@
       <c r="BI4" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BJ4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1550,18 +1601,30 @@
       <c r="BI5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1744,18 +1807,30 @@
       <c r="BI6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1775,7 +1850,7 @@
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="7"/>
@@ -1938,14 +2013,26 @@
       <c r="BI7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -1961,7 +2048,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2132,18 +2219,30 @@
       <c r="BI8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BJ8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BK8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BL8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2326,18 +2425,30 @@
       <c r="BI9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2353,7 +2464,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="6"/>
@@ -2520,18 +2631,30 @@
       <c r="BI10" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BJ10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BK10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM10" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2714,18 +2837,30 @@
       <c r="BI11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -2737,7 +2872,7 @@
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="5"/>
@@ -2908,18 +3043,30 @@
       <c r="BI12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM12" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -2931,7 +3078,7 @@
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="5"/>
@@ -3102,18 +3249,30 @@
       <c r="BI13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM13" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3125,7 +3284,7 @@
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="5"/>
@@ -3296,18 +3455,30 @@
       <c r="BI14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM14" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3490,18 +3661,30 @@
       <c r="BI15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3521,11 +3704,11 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3">
         <f t="shared" si="8"/>
@@ -3684,14 +3867,26 @@
       <c r="BI16" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BJ16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -3719,7 +3914,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="8"/>
@@ -3878,18 +4073,30 @@
       <c r="BI17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BJ17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BM17" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4072,18 +4279,30 @@
       <c r="BI18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -4095,7 +4314,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -4266,18 +4485,30 @@
       <c r="BI19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BL19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -4293,11 +4524,11 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="7"/>
@@ -4460,18 +4691,30 @@
       <c r="BI20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM20" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -4491,7 +4734,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -4654,14 +4897,26 @@
       <c r="BI21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -4677,7 +4932,7 @@
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
@@ -4685,11 +4940,11 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" si="8"/>
@@ -4848,14 +5103,26 @@
       <c r="BI22" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BJ22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BL22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM22" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -4871,7 +5138,7 @@
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="5"/>
@@ -4883,7 +5150,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="8"/>
@@ -5042,18 +5309,30 @@
       <c r="BI23" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BJ23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BK23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BL23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BM23" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="4"/>
@@ -5065,7 +5344,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -5234,20 +5513,32 @@
         <v>44</v>
       </c>
       <c r="BI24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM24" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -5430,18 +5721,30 @@
       <c r="BI25" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BJ25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -5624,18 +5927,30 @@
       <c r="BI26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -5812,18 +6127,30 @@
       <c r="BI27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -5994,18 +6321,30 @@
       <c r="BI28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -6122,14 +6461,26 @@
       <c r="BI29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -6145,7 +6496,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -6250,18 +6601,30 @@
       <c r="BI30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BJ30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BK30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BL30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -6378,15 +6741,30 @@
       <c r="BI31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BJ31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -6415,6 +6793,24 @@
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="46">COUNTIF(K32:VW32,"S")</f>
         <v>0</v>
+      </c>
+      <c r="BH32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BI32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM32" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EF626D-2241-854B-963D-7D8EB50A4343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23806D57-0ABD-4B40-853A-90C150BC7759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="54">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -587,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BO32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:67" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,18 +789,24 @@
       <c r="BM1" s="4">
         <v>46301</v>
       </c>
+      <c r="BN1" s="4">
+        <v>46302</v>
+      </c>
+      <c r="BO1" s="4">
+        <v>46303</v>
+      </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -995,18 +1001,24 @@
       <c r="BM2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1201,18 +1213,24 @@
       <c r="BM3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1407,18 +1425,24 @@
       <c r="BM4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1613,18 +1637,24 @@
       <c r="BM5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1819,18 +1849,24 @@
       <c r="BM6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2025,14 +2061,20 @@
       <c r="BM7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2048,7 +2090,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2231,18 +2273,24 @@
       <c r="BM8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2437,18 +2485,24 @@
       <c r="BM9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2456,7 +2510,7 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
@@ -2643,18 +2697,24 @@
       <c r="BM10" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BN10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO10" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2849,18 +2909,24 @@
       <c r="BM11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -3055,14 +3121,20 @@
       <c r="BM12" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
@@ -3078,7 +3150,7 @@
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="5"/>
@@ -3261,18 +3333,24 @@
       <c r="BM13" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO13" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3467,18 +3545,24 @@
       <c r="BM14" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3673,18 +3757,24 @@
       <c r="BM15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3879,14 +3969,20 @@
       <c r="BM16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -3914,7 +4010,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="8"/>
@@ -4085,18 +4181,24 @@
       <c r="BM17" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BN17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BO17" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4291,14 +4393,20 @@
       <c r="BM18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -4314,7 +4422,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -4497,14 +4605,20 @@
       <c r="BM19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -4524,7 +4638,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
@@ -4703,18 +4817,24 @@
       <c r="BM20" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BN20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BO20" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -4909,14 +5029,20 @@
       <c r="BM21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -4932,7 +5058,7 @@
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
@@ -5115,14 +5241,20 @@
       <c r="BM22" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO22" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
@@ -5150,7 +5282,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="8"/>
@@ -5321,14 +5453,20 @@
       <c r="BM23" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BN23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BO23" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5344,7 +5482,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -5527,18 +5665,24 @@
       <c r="BM24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -5733,18 +5877,24 @@
       <c r="BM25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -5939,18 +6089,24 @@
       <c r="BM26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO26" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6139,18 +6295,24 @@
       <c r="BM27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -6333,14 +6495,20 @@
       <c r="BM28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
@@ -6356,7 +6524,7 @@
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="16"/>
@@ -6473,14 +6641,20 @@
       <c r="BM29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO29" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
@@ -6496,7 +6670,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -6613,18 +6787,24 @@
       <c r="BM30" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BN30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO30" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -6753,18 +6933,24 @@
       <c r="BM31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BN31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:67" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -6810,6 +6996,12 @@
         <v>7</v>
       </c>
       <c r="BM32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BN32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BO32" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23806D57-0ABD-4B40-853A-90C150BC7759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB2A11-61A4-A942-AA71-0BE8A60C8763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="54">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -587,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BO32"/>
+  <dimension ref="A1:BR32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:70" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,18 +795,27 @@
       <c r="BO1" s="4">
         <v>46303</v>
       </c>
+      <c r="BP1" s="4">
+        <v>46304</v>
+      </c>
+      <c r="BQ1" s="4">
+        <v>46308</v>
+      </c>
+      <c r="BR1" s="4">
+        <v>46309</v>
+      </c>
     </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1007,18 +1016,27 @@
       <c r="BO2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1219,18 +1237,27 @@
       <c r="BO3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1431,18 +1458,27 @@
       <c r="BO4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1458,7 +1494,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="6"/>
@@ -1643,18 +1679,27 @@
       <c r="BO5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR5" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1855,18 +1900,27 @@
       <c r="BO6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -1878,7 +1932,7 @@
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="5"/>
@@ -2067,14 +2121,23 @@
       <c r="BO7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2090,7 +2153,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2279,18 +2342,27 @@
       <c r="BO8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BR8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2306,7 +2378,7 @@
       </c>
       <c r="G9" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="6"/>
@@ -2491,18 +2563,27 @@
       <c r="BO9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR9" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2703,18 +2784,27 @@
       <c r="BO10" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BP10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -2915,18 +3005,27 @@
       <c r="BO11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -3127,18 +3226,27 @@
       <c r="BO12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3162,7 +3270,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="8"/>
@@ -3339,18 +3447,27 @@
       <c r="BO13" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3551,18 +3668,27 @@
       <c r="BO14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3763,18 +3889,27 @@
       <c r="BO15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3975,14 +4110,23 @@
       <c r="BO16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4010,7 +4154,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="8"/>
@@ -4187,18 +4331,27 @@
       <c r="BO17" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BP17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR17" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="18" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4399,14 +4552,23 @@
       <c r="BO18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -4422,7 +4584,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -4611,18 +4773,27 @@
       <c r="BO19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BR19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -4638,7 +4809,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="6"/>
@@ -4823,18 +4994,27 @@
       <c r="BO20" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BP20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BQ20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -4842,7 +5022,7 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="1"/>
@@ -5035,18 +5215,27 @@
       <c r="BO21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BR21" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="22" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5058,7 +5247,7 @@
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
@@ -5247,18 +5436,27 @@
       <c r="BO22" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -5266,7 +5464,7 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
@@ -5459,14 +5657,23 @@
       <c r="BO23" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BP23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BQ23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5482,7 +5689,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -5671,18 +5878,27 @@
       <c r="BO24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BR24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -5883,18 +6099,27 @@
       <c r="BO25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="5">
         <f t="shared" si="4"/>
@@ -5906,7 +6131,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6095,18 +6320,27 @@
       <c r="BO26" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BR26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6114,7 +6348,7 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" ref="E27:E29" si="14">COUNTIF(K27:VS27,"A")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" ref="F27:F29" si="15">COUNTIF(K27:VT27,"B")</f>
@@ -6301,18 +6535,27 @@
       <c r="BO27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BQ27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -6501,18 +6744,27 @@
       <c r="BO28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -6524,7 +6776,7 @@
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="16"/>
@@ -6647,18 +6899,27 @@
       <c r="BO29" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BP29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -6670,7 +6931,7 @@
       </c>
       <c r="F30" s="3">
         <f t="shared" ref="F30" si="24">COUNTIF(K30:VT30,"B")</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" ref="G30" si="25">COUNTIF(K30:VU30,"M")</f>
@@ -6682,7 +6943,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="27">COUNTIF(K30:VW30,"RH")</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="28">COUNTIF(K30:VW30,"S")</f>
@@ -6782,29 +7043,38 @@
         <v>44</v>
       </c>
       <c r="BL30" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="BM30" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="BN30" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="BO30" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
+      </c>
+      <c r="BP30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR30" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -6939,18 +7209,27 @@
       <c r="BO31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BP31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:67" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7002,6 +7281,15 @@
         <v>7</v>
       </c>
       <c r="BO32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR32" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB2A11-61A4-A942-AA71-0BE8A60C8763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D000F9-2BF5-9C4D-BC70-77E61A83E26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="54">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -587,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BR32"/>
+  <dimension ref="A1:BT32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:72" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,18 +804,24 @@
       <c r="BR1" s="4">
         <v>46309</v>
       </c>
+      <c r="BS1" s="4">
+        <v>46310</v>
+      </c>
+      <c r="BT1" s="4">
+        <v>46311</v>
+      </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1025,18 +1031,24 @@
       <c r="BR2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1246,18 +1258,24 @@
       <c r="BR3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1467,14 +1485,20 @@
       <c r="BR4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
@@ -1494,7 +1518,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="6"/>
@@ -1688,18 +1712,24 @@
       <c r="BR5" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BS5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BT5" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1909,14 +1939,20 @@
       <c r="BR6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
@@ -1936,7 +1972,7 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="6"/>
@@ -2130,14 +2166,20 @@
       <c r="BR7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BT7" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2153,7 +2195,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2351,18 +2393,24 @@
       <c r="BR8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BS8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BT8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2572,18 +2620,24 @@
       <c r="BR9" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BS9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2793,18 +2847,24 @@
       <c r="BR10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3014,18 +3074,24 @@
       <c r="BR11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" si="4"/>
@@ -3235,18 +3301,24 @@
       <c r="BR12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3456,18 +3528,24 @@
       <c r="BR13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3677,18 +3755,24 @@
       <c r="BR14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3708,7 +3792,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -3898,18 +3982,24 @@
       <c r="BR15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT15" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -3929,7 +4019,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="7"/>
@@ -4119,14 +4209,20 @@
       <c r="BR16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT16" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="17" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4154,7 +4250,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="8"/>
@@ -4340,18 +4436,24 @@
       <c r="BR17" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BS17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BT17" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="18" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4561,14 +4663,20 @@
       <c r="BR18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -4584,7 +4692,7 @@
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="5"/>
@@ -4782,18 +4890,24 @@
       <c r="BR19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BS19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BT19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="20" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -5003,14 +5117,20 @@
       <c r="BR20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
@@ -5022,7 +5142,7 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="1"/>
@@ -5224,18 +5344,24 @@
       <c r="BR21" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BS21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BT21" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="22" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5255,7 +5381,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -5445,18 +5571,24 @@
       <c r="BR22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT22" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="23" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -5666,14 +5798,20 @@
       <c r="BR23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5689,7 +5827,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -5887,18 +6025,24 @@
       <c r="BR24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BS24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BT24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6108,14 +6252,20 @@
       <c r="BR25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6131,7 +6281,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6329,18 +6479,24 @@
       <c r="BR26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BS26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BT26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6544,18 +6700,24 @@
       <c r="BR27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -6753,18 +6915,24 @@
       <c r="BR28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -6908,22 +7076,28 @@
       <c r="BR29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="3">
         <f t="shared" ref="E30" si="23">COUNTIF(K30:VS30,"A")</f>
@@ -7063,18 +7237,24 @@
       <c r="BR30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="BT30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D31" s="5">
         <f t="shared" ref="D31" si="31">COUNTIF(K31:VR31,"REP")</f>
@@ -7218,18 +7398,24 @@
       <c r="BR31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BS31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT31" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="32" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7290,6 +7476,12 @@
         <v>7</v>
       </c>
       <c r="BR32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT32" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D000F9-2BF5-9C4D-BC70-77E61A83E26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002A0785-B4C1-0E49-BDF7-DE32AAE1FB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="54">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -587,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BT32"/>
+  <dimension ref="A1:BU32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:73" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,18 +810,21 @@
       <c r="BT1" s="4">
         <v>46311</v>
       </c>
+      <c r="BU1" s="4">
+        <v>46314</v>
+      </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1037,18 +1040,21 @@
       <c r="BT2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1264,18 +1270,21 @@
       <c r="BT3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1491,18 +1500,21 @@
       <c r="BT4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1718,18 +1730,21 @@
       <c r="BT5" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BU5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1945,18 +1960,21 @@
       <c r="BT6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2172,14 +2190,17 @@
       <c r="BT7" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BU7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2195,7 +2216,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2399,18 +2420,21 @@
       <c r="BT8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BU8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2626,14 +2650,17 @@
       <c r="BT9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
@@ -2645,7 +2672,7 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
@@ -2853,18 +2880,21 @@
       <c r="BT10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU10" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3080,14 +3110,17 @@
       <c r="BT11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -3103,7 +3136,7 @@
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="5"/>
@@ -3307,18 +3340,21 @@
       <c r="BT12" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU12" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3534,18 +3570,21 @@
       <c r="BT13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3761,18 +3800,21 @@
       <c r="BT14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3988,18 +4030,21 @@
       <c r="BT15" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BU15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -4215,14 +4260,17 @@
       <c r="BT16" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BU16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4238,7 +4286,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -4442,18 +4490,21 @@
       <c r="BT17" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BU17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4669,14 +4720,17 @@
       <c r="BT18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -4704,7 +4758,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="8"/>
@@ -4896,14 +4950,17 @@
       <c r="BT19" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BU19" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
@@ -4915,7 +4972,7 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
@@ -5123,18 +5180,21 @@
       <c r="BT20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU20" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="21" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -5350,18 +5410,21 @@
       <c r="BT21" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BU21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5577,18 +5640,21 @@
       <c r="BT22" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="BU22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -5804,14 +5870,17 @@
       <c r="BT23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5827,7 +5896,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -6031,18 +6100,21 @@
       <c r="BT24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BU24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6258,14 +6330,17 @@
       <c r="BT25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6281,7 +6356,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6485,18 +6560,21 @@
       <c r="BT26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BU26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6706,18 +6784,21 @@
       <c r="BT27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -6921,14 +7002,17 @@
       <c r="BT28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
@@ -6940,7 +7024,7 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="15"/>
@@ -7082,18 +7166,21 @@
       <c r="BT29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU29" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="30" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -7243,14 +7330,17 @@
       <c r="BT30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -7262,7 +7352,7 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" ref="E31" si="32">COUNTIF(K31:VS31,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
@@ -7404,18 +7494,21 @@
       <c r="BT31" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BU31" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7482,6 +7575,9 @@
         <v>7</v>
       </c>
       <c r="BT32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU32" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002A0785-B4C1-0E49-BDF7-DE32AAE1FB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB8EC9B-7661-5942-91C9-24AEE05281DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="55">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Glenn Manga-Tabi</t>
+  </si>
+  <si>
+    <t>Jeremy Romany</t>
   </si>
 </sst>
 </file>
@@ -587,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BU32"/>
+  <dimension ref="A1:BV33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:74" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -813,18 +816,21 @@
       <c r="BU1" s="4">
         <v>46314</v>
       </c>
+      <c r="BV1" s="4">
+        <v>46315</v>
+      </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1043,18 +1049,21 @@
       <c r="BU2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1273,18 +1282,21 @@
       <c r="BU3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="4"/>
@@ -1296,7 +1308,7 @@
       </c>
       <c r="F4" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="5"/>
@@ -1501,20 +1513,23 @@
         <v>7</v>
       </c>
       <c r="BU4" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1733,18 +1748,21 @@
       <c r="BU5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1963,18 +1981,21 @@
       <c r="BU6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2193,14 +2214,17 @@
       <c r="BU7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2216,7 +2240,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2423,18 +2447,21 @@
       <c r="BU8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BV8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2653,18 +2680,21 @@
       <c r="BU9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2883,18 +2913,21 @@
       <c r="BU10" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BV10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3113,14 +3146,17 @@
       <c r="BU11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -3132,7 +3168,7 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
@@ -3343,18 +3379,21 @@
       <c r="BU12" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BV12" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3573,18 +3612,21 @@
       <c r="BU13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3803,18 +3845,21 @@
       <c r="BU14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -4033,18 +4078,21 @@
       <c r="BU15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -4263,14 +4311,17 @@
       <c r="BU16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4286,7 +4337,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -4493,18 +4544,21 @@
       <c r="BU17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BV17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4723,14 +4777,17 @@
       <c r="BU18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
@@ -4758,7 +4815,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="8"/>
@@ -4953,18 +5010,21 @@
       <c r="BU19" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BV19" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -5183,18 +5243,21 @@
       <c r="BU20" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BV20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -5413,18 +5476,21 @@
       <c r="BU21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5643,18 +5709,21 @@
       <c r="BU22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -5873,14 +5942,17 @@
       <c r="BU23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5896,7 +5968,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -6103,18 +6175,21 @@
       <c r="BU24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BV24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6333,14 +6408,17 @@
       <c r="BU25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6356,7 +6434,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6563,18 +6641,21 @@
       <c r="BU26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BV26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6787,18 +6868,21 @@
       <c r="BU27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -7005,18 +7089,21 @@
       <c r="BU28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -7169,18 +7256,21 @@
       <c r="BU29" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BV29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -7333,14 +7423,17 @@
       <c r="BU30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BV30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -7352,7 +7445,7 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" ref="E31" si="32">COUNTIF(K31:VS31,"A")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
@@ -7497,18 +7590,21 @@
       <c r="BU31" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BV31" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="32" spans="1:73" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7578,6 +7674,29 @@
         <v>7</v>
       </c>
       <c r="BU32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV32" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="BR33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BS33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BT33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BV33" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB8EC9B-7661-5942-91C9-24AEE05281DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949541F1-0B8C-7D41-923F-87EF7791B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="55">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -590,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BV33"/>
+  <dimension ref="A1:BY33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:77" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,18 +819,27 @@
       <c r="BV1" s="4">
         <v>46315</v>
       </c>
+      <c r="BW1" s="4">
+        <v>46316</v>
+      </c>
+      <c r="BX1" s="4">
+        <v>46318</v>
+      </c>
+      <c r="BY1" s="4">
+        <v>46321</v>
+      </c>
     </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1052,18 +1061,27 @@
       <c r="BV2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1285,14 +1303,23 @@
       <c r="BV3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
@@ -1308,11 +1335,11 @@
       </c>
       <c r="F4" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="6"/>
@@ -1518,18 +1545,27 @@
       <c r="BV4" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BW4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BY4" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1751,18 +1787,27 @@
       <c r="BV5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -1984,18 +2029,27 @@
       <c r="BV6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2217,14 +2271,23 @@
       <c r="BV7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2240,7 +2303,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2450,18 +2513,27 @@
       <c r="BV8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BW8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BY8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2683,18 +2755,27 @@
       <c r="BV9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -2916,18 +2997,27 @@
       <c r="BV10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3149,14 +3239,23 @@
       <c r="BV11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -3168,7 +3267,7 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
@@ -3382,18 +3481,27 @@
       <c r="BV12" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BW12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BX12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BY12" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3615,18 +3723,27 @@
       <c r="BV13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3642,7 +3759,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="6"/>
@@ -3848,18 +3965,27 @@
       <c r="BV14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BY14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -3879,7 +4005,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="7"/>
@@ -4081,18 +4207,27 @@
       <c r="BV15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BY15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -4314,14 +4449,23 @@
       <c r="BV16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4337,7 +4481,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -4547,18 +4691,27 @@
       <c r="BV17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BW17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BY17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4780,18 +4933,27 @@
       <c r="BV18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -4815,7 +4977,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="8"/>
@@ -5013,18 +5175,27 @@
       <c r="BV19" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="BW19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BX19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BY19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -5246,18 +5417,27 @@
       <c r="BV20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -5277,7 +5457,7 @@
       </c>
       <c r="H21" s="3">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="7"/>
@@ -5479,18 +5659,27 @@
       <c r="BV21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BY21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5506,11 +5695,11 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="7"/>
@@ -5712,18 +5901,27 @@
       <c r="BV22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BY22" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="23" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -5945,14 +6143,23 @@
       <c r="BV23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -5968,7 +6175,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -6178,18 +6385,27 @@
       <c r="BV24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BW24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BY24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6411,14 +6627,23 @@
       <c r="BV25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6434,7 +6659,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6644,18 +6869,27 @@
       <c r="BV26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BW26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="BY26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -6871,18 +7105,27 @@
       <c r="BV27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -7092,18 +7335,27 @@
       <c r="BV28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -7259,18 +7511,27 @@
       <c r="BV29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -7426,14 +7687,23 @@
       <c r="BV30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -7445,7 +7715,7 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" ref="E31" si="32">COUNTIF(K31:VS31,"A")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
@@ -7593,18 +7863,27 @@
       <c r="BV31" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BW31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BX31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="BY31" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="32" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7679,8 +7958,17 @@
       <c r="BV32" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BW32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY32" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="33" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -7697,6 +7985,15 @@
         <v>7</v>
       </c>
       <c r="BV33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY33" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949541F1-0B8C-7D41-923F-87EF7791B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA8E09F-90FD-E448-BCC3-CC56F09BE58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="55">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -590,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BY33"/>
+  <dimension ref="A1:BZ33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:78" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -828,18 +828,21 @@
       <c r="BY1" s="4">
         <v>46321</v>
       </c>
+      <c r="BZ1" s="4">
+        <v>46322</v>
+      </c>
     </row>
-    <row r="2" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1070,18 +1073,21 @@
       <c r="BY2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1312,14 +1318,17 @@
       <c r="BY3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
@@ -1339,7 +1348,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="6"/>
@@ -1554,18 +1563,21 @@
       <c r="BY4" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BZ4" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1796,18 +1808,21 @@
       <c r="BY5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -2038,18 +2053,21 @@
       <c r="BY6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2280,14 +2298,17 @@
       <c r="BY7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2303,7 +2324,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2522,18 +2543,21 @@
       <c r="BY8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BZ8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2764,18 +2788,21 @@
       <c r="BY9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -3006,18 +3033,21 @@
       <c r="BY10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3248,14 +3278,17 @@
       <c r="BY11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -3267,7 +3300,7 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
@@ -3490,18 +3523,21 @@
       <c r="BY12" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BZ12" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3732,18 +3768,21 @@
       <c r="BY13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -3974,18 +4013,21 @@
       <c r="BY14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -4216,14 +4258,17 @@
       <c r="BY15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
@@ -4243,7 +4288,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="6"/>
@@ -4458,14 +4503,17 @@
       <c r="BY16" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ16" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="17" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4481,7 +4529,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -4700,18 +4748,21 @@
       <c r="BY17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BZ17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4942,18 +4993,21 @@
       <c r="BY18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -5184,18 +5238,21 @@
       <c r="BY19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -5426,18 +5483,21 @@
       <c r="BY20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -5668,18 +5728,21 @@
       <c r="BY21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="5">
         <f t="shared" si="4"/>
@@ -5910,18 +5973,21 @@
       <c r="BY22" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="BZ22" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="23" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -6152,14 +6218,17 @@
       <c r="BY23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -6175,7 +6244,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -6394,18 +6463,21 @@
       <c r="BY24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BZ24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6636,14 +6708,17 @@
       <c r="BY25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6659,7 +6734,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6878,18 +6953,21 @@
       <c r="BY26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="BZ26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -7114,18 +7192,21 @@
       <c r="BY27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -7344,18 +7425,21 @@
       <c r="BY28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -7520,18 +7604,21 @@
       <c r="BY29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -7696,14 +7783,17 @@
       <c r="BY30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3">
         <f t="shared" ref="B31" si="29">COUNTA(K31:VR31)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" ref="C31" si="30">COUNTIF(K31:VR31,"P")</f>
@@ -7715,7 +7805,7 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" ref="E31" si="32">COUNTIF(K31:VS31,"A")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" ref="F31" si="33">COUNTIF(K31:VT31,"B")</f>
@@ -7872,18 +7962,21 @@
       <c r="BY31" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="BZ31" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="32" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -7967,8 +8060,11 @@
       <c r="BY32" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="BZ32" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="33" spans="1:77" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -7994,6 +8090,9 @@
         <v>7</v>
       </c>
       <c r="BY33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BZ33" s="3" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/2026-2027/Présences.xlsx
+++ b/data/2026-2027/Présences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA8E09F-90FD-E448-BCC3-CC56F09BE58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F717D-0818-F64E-AB8C-6E1D8C8B1D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{2EF0EE96-8EE0-C649-8161-B8679CB6F342}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="55">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -590,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0866E353-69CC-CA42-AE0E-F860DC308060}">
-  <dimension ref="A1:BZ33"/>
+  <dimension ref="A1:CA33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:79" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -831,18 +831,21 @@
       <c r="BZ1" s="4">
         <v>46322</v>
       </c>
+      <c r="CA1" s="4">
+        <v>46323</v>
+      </c>
     </row>
-    <row r="2" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <f>COUNTA(K2:VR2)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3">
         <f>COUNTIF(K2:VR2,"P")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="5">
         <f>COUNTIF(K2:VR2,"REP")</f>
@@ -1076,18 +1079,21 @@
       <c r="BZ2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA2" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <f t="shared" ref="B3:B21" si="2">COUNTA(K3:VR3)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C21" si="3">COUNTIF(K3:VR3,"P")</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" ref="D3:D26" si="4">COUNTIF(K3:VR3,"REP")</f>
@@ -1321,14 +1327,17 @@
       <c r="BZ3" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="3"/>
@@ -1348,7 +1357,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="6"/>
@@ -1566,18 +1575,21 @@
       <c r="BZ4" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="CA4" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="5" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="4"/>
@@ -1811,18 +1823,21 @@
       <c r="BZ5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="3"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="5">
         <f t="shared" si="4"/>
@@ -2056,18 +2071,21 @@
       <c r="BZ6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5">
         <f t="shared" si="4"/>
@@ -2301,14 +2319,17 @@
       <c r="BZ7" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA7" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="8" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="3"/>
@@ -2324,7 +2345,7 @@
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="5"/>
@@ -2546,18 +2567,21 @@
       <c r="BZ8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="CA8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="5">
         <f t="shared" si="4"/>
@@ -2791,18 +2815,21 @@
       <c r="BZ9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="5">
         <f t="shared" si="4"/>
@@ -3036,18 +3063,21 @@
       <c r="BZ10" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA10" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" si="4"/>
@@ -3281,14 +3311,17 @@
       <c r="BZ11" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA11" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -3300,7 +3333,7 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
@@ -3526,18 +3559,21 @@
       <c r="BZ12" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="CA12" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" si="4"/>
@@ -3771,18 +3807,21 @@
       <c r="BZ13" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" si="4"/>
@@ -4016,18 +4055,21 @@
       <c r="BZ14" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA14" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="15" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="4"/>
@@ -4261,18 +4303,21 @@
       <c r="BZ15" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA15" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="16" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" si="4"/>
@@ -4506,14 +4551,17 @@
       <c r="BZ16" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="CA16" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="3"/>
@@ -4529,7 +4577,7 @@
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="5"/>
@@ -4751,18 +4799,21 @@
       <c r="BZ17" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="CA17" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" si="4"/>
@@ -4996,18 +5047,21 @@
       <c r="BZ18" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA18" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="19" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" si="4"/>
@@ -5241,18 +5295,21 @@
       <c r="BZ19" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA19" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="5">
         <f t="shared" si="4"/>
@@ -5486,18 +5543,21 @@
       <c r="BZ20" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA20" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="21" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="4"/>
@@ -5731,14 +5791,17 @@
       <c r="BZ21" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA21" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="22" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="3">
         <f t="shared" ref="B22:B26" si="9">COUNTA(K22:VR22)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" ref="C22:C26" si="10">COUNTIF(K22:VR22,"P")</f>
@@ -5754,7 +5817,7 @@
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
@@ -5976,18 +6039,21 @@
       <c r="BZ22" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA22" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="23" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="3">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="4"/>
@@ -6221,14 +6287,17 @@
       <c r="BZ23" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA23" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="24" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="3">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="10"/>
@@ -6244,7 +6313,7 @@
       </c>
       <c r="F24" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="5"/>
@@ -6466,18 +6535,21 @@
       <c r="BZ24" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="CA24" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="25" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="3">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="10"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5">
         <f t="shared" si="4"/>
@@ -6711,14 +6783,17 @@
       <c r="BZ25" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA25" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="26" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="3">
         <f t="shared" si="9"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="10"/>
@@ -6734,7 +6809,7 @@
       </c>
       <c r="F26" s="3">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="5"/>
@@ -6956,18 +7031,21 @@
       <c r="BZ26" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="CA26" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="27" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="3">
         <f t="shared" ref="B27:B29" si="11">COUNTA(K27:VR27)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" ref="C27:C29" si="12">COUNTIF(K27:VR27,"P")</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="5">
         <f t="shared" ref="D27:D29" si="13">COUNTIF(K27:VR27,"REP")</f>
@@ -7195,18 +7273,21 @@
       <c r="BZ27" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA27" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="3">
         <f t="shared" si="11"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="12"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="5">
         <f t="shared" si="13"/>
@@ -7428,18 +7509,21 @@
       <c r="BZ28" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA28" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="29" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3">
         <f t="shared" si="11"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="12"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D29" s="5">
         <f t="shared" si="13"/>
@@ -7607,18 +7691,21 @@
       <c r="BZ29" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA29" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3">
         <f t="shared" ref="B30" si="20">COUNTA(K30:VR30)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" ref="C30" si="21">COUNTIF(K30:VR30,"P")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="5">
         <f t="shared" ref="D30" si="22">COUNTIF(K30:VR30,"REP")</f>
@@ -7786,8 +7873,11 @@
       <c r="BZ30" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA30" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="31" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -7965,18 +8055,19 @@
       <c r="BZ31" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="CA31" s="3"/>
     </row>
-    <row r="32" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3">
         <f t="shared" ref="B32" si="38">COUNTA(K32:VR32)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" ref="C32" si="39">COUNTIF(K32:VR32,"P")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="5">
         <f t="shared" ref="D32" si="40">COUNTIF(K32:VR32,"REP")</f>
@@ -8063,8 +8154,11 @@
       <c r="BZ32" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="CA32" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="33" spans="1:78" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -8093,6 +8187,9 @@
         <v>7</v>
       </c>
       <c r="BZ33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA33" s="3" t="s">
         <v>7</v>
       </c>
     </row>
